--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
         <v>4.2</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N77" t="n">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="M81" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M116" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N116" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,55 +14344,55 @@
         </is>
       </c>
       <c r="L117" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M117" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N117" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB117" t="n">
         <v>2.12</v>
-      </c>
-      <c r="M117" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N117" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" t="n">
-        <v>0</v>
-      </c>
-      <c r="W117" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA117" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="M118" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16406,10 +16406,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16763,10 +16763,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z137" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="M142" t="n">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
       <c r="N142" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD142" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="M143" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="N143" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17914,55 +17914,55 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="M147" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="N147" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
         <v>2.1</v>
       </c>
-      <c r="O147" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" t="n">
-        <v>0</v>
-      </c>
-      <c r="T147" t="n">
-        <v>0</v>
-      </c>
-      <c r="U147" t="n">
-        <v>0</v>
-      </c>
-      <c r="V147" t="n">
-        <v>0</v>
-      </c>
-      <c r="W147" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>2.13</v>
-      </c>
       <c r="AB147" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="M57" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7.4</v>
+        <v>1.78</v>
       </c>
       <c r="M58" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="M116" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N116" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="M118" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N118" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="M127" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N127" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16406,10 +16406,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M137" t="n">
         <v>3.15</v>
       </c>
-      <c r="M137" t="n">
-        <v>2.9</v>
-      </c>
       <c r="N137" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16763,16 +16763,16 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G145" t="n">

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.4</v>
+        <v>1.78</v>
       </c>
       <c r="M57" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="M58" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M117" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N117" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M118" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N118" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7.4</v>
+        <v>1.25</v>
       </c>
       <c r="M58" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="N58" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.25</v>
+        <v>7.4</v>
       </c>
       <c r="M59" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>1.42</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="M93" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="M94" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N117" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M118" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N118" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G133" t="n">

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.8</v>
+        <v>2.23</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>3.28</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G115" t="n">

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="N11" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="M57" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M58" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.45</v>
+        <v>2.03</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7.4</v>
+        <v>1.25</v>
       </c>
       <c r="M59" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="N59" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,14 +8632,14 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="M69" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N69" t="n">
         <v>4.2</v>
       </c>
-      <c r="N69" t="n">
-        <v>6.8</v>
-      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,55 +14225,55 @@
         </is>
       </c>
       <c r="L116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB116" t="n">
         <v>2.12</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N116" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="M117" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N117" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB117" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="M118" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="M126" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N126" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15811,10 +15811,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16406,10 +16406,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="N31" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.4</v>
+        <v>1.25</v>
       </c>
       <c r="M57" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="N57" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="M58" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M59" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.45</v>
+        <v>2.03</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M116" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N116" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,55 +14463,55 @@
         </is>
       </c>
       <c r="L118" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N118" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB118" t="n">
         <v>2.12</v>
-      </c>
-      <c r="M118" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N118" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M129" t="n">
         <v>3.15</v>
       </c>
-      <c r="M129" t="n">
-        <v>2.9</v>
-      </c>
       <c r="N129" t="n">
-        <v>2.45</v>
+        <v>2.95</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15811,16 +15811,16 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16049,10 +16049,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16132,10 +16132,10 @@
         <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N132" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="M137" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N137" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="M142" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="N142" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="M143" t="n">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
       <c r="N143" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD143" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M57" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.45</v>
+        <v>2.03</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7.4</v>
+        <v>1.25</v>
       </c>
       <c r="M58" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="N58" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.78</v>
+        <v>7.4</v>
       </c>
       <c r="M59" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N59" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.47</v>
+        <v>2.21</v>
       </c>
       <c r="M96" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="N96" t="n">
-        <v>6.8</v>
+        <v>3.15</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16049,10 +16049,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16132,10 +16132,10 @@
         <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16525,10 +16525,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="M142" t="n">
-        <v>4.4</v>
+        <v>6.9</v>
       </c>
       <c r="N142" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD142" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="M143" t="n">
-        <v>6.9</v>
+        <v>4.4</v>
       </c>
       <c r="N143" t="n">
-        <v>11.5</v>
+        <v>6.8</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
         <v>3.65</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="M57" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.03</v>
+        <v>1.45</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="M58" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.45</v>
+        <v>2.03</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N78" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,55 +14225,55 @@
         </is>
       </c>
       <c r="L116" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB116" t="n">
         <v>2.12</v>
-      </c>
-      <c r="M116" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N116" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M118" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.68</v>
+        <v>3.15</v>
       </c>
       <c r="M130" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N130" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,16 +15930,16 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16132,10 +16132,10 @@
         <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N132" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="M135" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N135" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16525,16 +16525,16 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.8</v>
+        <v>3.81</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7204,10 +7204,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M57" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="N57" t="n">
         <v>11</v>
@@ -7323,10 +7323,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="M58" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="N58" t="n">
         <v>4.7</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="M65" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="M68" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="M73" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="N73" t="n">
-        <v>1.87</v>
+        <v>3.15</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.76</v>
+        <v>2.26</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N101" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="M116" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>4.7</v>
+        <v>3.59</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="M117" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N117" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,55 +14463,55 @@
         </is>
       </c>
       <c r="L118" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N118" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB118" t="n">
         <v>2.12</v>
-      </c>
-      <c r="M118" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N118" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" t="n">
-        <v>0</v>
-      </c>
-      <c r="W118" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA118" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="M128" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N128" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16132,10 +16132,10 @@
         <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,10 +16644,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="M142" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="N142" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17370,7 +17370,7 @@
         <v>2.75</v>
       </c>
       <c r="AC142" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD142" t="n">
         <v>1.8</v>
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M143" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N143" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>3.81</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="M57" t="n">
-        <v>6.3</v>
+        <v>3.61</v>
       </c>
       <c r="N57" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="M58" t="n">
-        <v>3.61</v>
+        <v>6.3</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="M63" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.07</v>
+        <v>3.75</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="M81" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="M82" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N83" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="M85" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N85" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="M86" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N86" t="n">
-        <v>2.37</v>
+        <v>4.9</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="M88" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N88" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N89" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N92" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N96" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.82</v>
+        <v>2.95</v>
       </c>
       <c r="M99" t="n">
         <v>3.4</v>
       </c>
       <c r="N99" t="n">
-        <v>4.2</v>
+        <v>2.29</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="M129" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="N129" t="n">
-        <v>3.11</v>
+        <v>4.6</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16049,10 +16049,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="M136" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N136" t="n">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,16 +16644,16 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="M39" t="n">
         <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>3.7</v>
+        <v>2.11</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="M61" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,14 +7918,14 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="M63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N63" t="n">
         <v>3.15</v>
       </c>
-      <c r="N63" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="M66" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N70" t="n">
-        <v>1.87</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.01</v>
+        <v>2.55</v>
       </c>
       <c r="M75" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N80" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.82</v>
+        <v>2.39</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="M83" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N83" t="n">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N84" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="M85" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>2.37</v>
+        <v>3.45</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.66</v>
+        <v>2.95</v>
       </c>
       <c r="M86" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N86" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M87" t="n">
         <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="M88" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>4.5</v>
+        <v>2.49</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="M89" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>2.35</v>
+        <v>3.75</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,14 +11131,14 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="M90" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N90" t="n">
         <v>3.5</v>
       </c>
-      <c r="N90" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="M91" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="M92" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N92" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.47</v>
+        <v>2.33</v>
       </c>
       <c r="M93" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>6.8</v>
+        <v>2.85</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.85</v>
+        <v>1.47</v>
       </c>
       <c r="M95" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N95" t="n">
-        <v>2.49</v>
+        <v>6.8</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="M96" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N116" t="n">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="M118" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="M127" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="N127" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16049,10 +16049,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.68</v>
+        <v>3.12</v>
       </c>
       <c r="M136" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="N136" t="n">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,16 +16644,16 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA136" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,14 +17319,14 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="M142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N142" t="n">
         <v>6.5</v>
       </c>
-      <c r="N142" t="n">
-        <v>13</v>
-      </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="M143" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N143" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD143" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="M31" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N31" t="n">
         <v>3.65</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.73</v>
+        <v>7.4</v>
       </c>
       <c r="M57" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="M58" t="n">
-        <v>6.3</v>
+        <v>3.61</v>
       </c>
       <c r="N58" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7.4</v>
+        <v>1.23</v>
       </c>
       <c r="M59" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="N59" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="M61" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N61" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.9</v>
+        <v>1.86</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>2.35</v>
+        <v>4.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.75</v>
+        <v>2.01</v>
       </c>
       <c r="M65" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N65" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N65" t="n">
-        <v>1.93</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.82</v>
+        <v>2.39</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N67" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="M70" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="M76" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N76" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N79" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="M80" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.39</v>
+        <v>2.85</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N81" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="M83" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N83" t="n">
-        <v>1.87</v>
+        <v>6.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.66</v>
+        <v>2.95</v>
       </c>
       <c r="M84" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.95</v>
+        <v>1.66</v>
       </c>
       <c r="M86" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N86" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N87" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.85</v>
+        <v>1.82</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>2.49</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N89" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="M92" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N92" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
         <v>3.5</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
         <v>3.5</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16251,10 +16251,10 @@
         <v>1.68</v>
       </c>
       <c r="M133" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N133" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.4</v>
+        <v>1.73</v>
       </c>
       <c r="M57" t="n">
-        <v>4.4</v>
+        <v>3.61</v>
       </c>
       <c r="N57" t="n">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="M58" t="n">
-        <v>3.61</v>
+        <v>6.3</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.23</v>
+        <v>7.4</v>
       </c>
       <c r="M59" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>1.42</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="M65" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AB66" t="n">
         <v>1.68</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.39</v>
+        <v>2.01</v>
       </c>
       <c r="M67" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N67" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="M69" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N69" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.77</v>
+        <v>2.85</v>
       </c>
       <c r="M72" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>2.49</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>4</v>
+        <v>2.13</v>
       </c>
       <c r="M76" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N76" t="n">
-        <v>1.87</v>
+        <v>3.25</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,14 +9584,14 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="M77" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N77" t="n">
         <v>3.15</v>
       </c>
-      <c r="N77" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N80" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="M81" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N81" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="N82" t="n">
-        <v>2.49</v>
+        <v>4.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="M83" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N84" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="M85" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N85" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="M86" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N86" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M87" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="M89" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>1.93</v>
+        <v>4.3</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="M92" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N92" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,55 +11845,55 @@
         </is>
       </c>
       <c r="L96" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M96" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB96" t="n">
         <v>2</v>
-      </c>
-      <c r="M96" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N96" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>1.62</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.68</v>
+        <v>3.55</v>
       </c>
       <c r="M97" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N97" t="n">
-        <v>4.9</v>
+        <v>1.95</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.13</v>
+        <v>2.8</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="M116" t="n">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="N116" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M117" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N118" t="n">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="N125" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15811,10 +15811,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M133" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="N133" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,16 +16293,16 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="AC133" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD133" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16370,10 +16370,10 @@
         <v>1.68</v>
       </c>
       <c r="M134" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N134" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,10 +16644,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="M138" t="n">
         <v>3.8</v>
       </c>
       <c r="N138" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="M142" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N142" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD142" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,14 +17438,14 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="M143" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N143" t="n">
         <v>6.5</v>
       </c>
-      <c r="N143" t="n">
-        <v>13</v>
-      </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G146" t="n">

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N62" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N66" t="n">
         <v>3.15</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="M67" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="M69" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.68</v>
+        <v>2.9</v>
       </c>
       <c r="M71" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>4.9</v>
+        <v>2.35</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.95</v>
+        <v>1.96</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.29</v>
+        <v>3.75</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="M77" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="N77" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="M80" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>1.47</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N81" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.82</v>
+        <v>2.8</v>
       </c>
       <c r="M82" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N82" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         <v>2</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="M85" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N85" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="M86" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N86" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>2.49</v>
+        <v>3.15</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N89" t="n">
-        <v>4.3</v>
+        <v>2.49</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.33</v>
+        <v>3.55</v>
       </c>
       <c r="M90" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N90" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="M91" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.47</v>
+        <v>2.07</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N92" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="M93" t="n">
         <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N94" t="n">
-        <v>1.93</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="M95" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N95" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="M96" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N96" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N98" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="M116" t="n">
-        <v>3.21</v>
+        <v>3.72</v>
       </c>
       <c r="N116" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N117" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="M118" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M125" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="M128" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="N128" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="M129" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N129" t="n">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15811,16 +15811,16 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,16 +16174,16 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.72</v>
+        <v>3.12</v>
       </c>
       <c r="M133" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="N133" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16287,22 +16287,22 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD133" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,14 +17319,14 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="M142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N142" t="n">
         <v>6.5</v>
       </c>
-      <c r="N142" t="n">
-        <v>13</v>
-      </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="M143" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N143" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD143" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.85</v>
+        <v>2.13</v>
       </c>
       <c r="M61" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M65" t="n">
         <v>2.95</v>
       </c>
-      <c r="M65" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N65" t="n">
-        <v>2.29</v>
+        <v>3.15</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="M66" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.96</v>
+        <v>3.75</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.39</v>
+        <v>1.77</v>
       </c>
       <c r="M75" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.72</v>
+        <v>2.55</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M78" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N78" t="n">
         <v>3.75</v>
-      </c>
-      <c r="M78" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N78" t="n">
-        <v>1.93</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="M79" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N79" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M82" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="M85" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="M86" t="n">
         <v>3.15</v>
       </c>
       <c r="N86" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M87" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N87" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10822,7 +10822,7 @@
         <v>2.2</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M88" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N88" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="M89" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N89" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.55</v>
+        <v>2.33</v>
       </c>
       <c r="M90" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N91" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="M94" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N94" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="M95" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N95" t="n">
-        <v>2.37</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="M96" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N96" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="M98" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N98" t="n">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.82</v>
+        <v>2.9</v>
       </c>
       <c r="M99" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>4.3</v>
+        <v>2.37</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="M116" t="n">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="N116" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M117" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N118" t="n">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M128" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N128" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16287,10 +16287,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,10 +16644,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>3.81</v>
       </c>
       <c r="M29" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.44</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="M57" t="n">
-        <v>3.61</v>
+        <v>6.3</v>
       </c>
       <c r="N57" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="M58" t="n">
-        <v>6.3</v>
+        <v>3.61</v>
       </c>
       <c r="N58" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,16 +7368,16 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.55</v>
+        <v>1.77</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N61" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="M65" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>2.55</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="M72" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N75" t="n">
         <v>4.3</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.82</v>
+        <v>2.95</v>
       </c>
       <c r="M76" t="n">
         <v>3.4</v>
       </c>
       <c r="N76" t="n">
-        <v>4.2</v>
+        <v>2.29</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="M77" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N77" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.96</v>
+        <v>2.85</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N78" t="n">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N83" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="M86" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N86" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="M88" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N89" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="M90" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N90" t="n">
         <v>3.45</v>
-      </c>
-      <c r="N90" t="n">
-        <v>2.85</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="M93" t="n">
         <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="M94" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N94" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="M95" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N95" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.82</v>
+        <v>2.33</v>
       </c>
       <c r="M96" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N96" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.85</v>
+        <v>1.66</v>
       </c>
       <c r="M98" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N98" t="n">
-        <v>2.49</v>
+        <v>4.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="M116" t="n">
-        <v>3.21</v>
+        <v>3.72</v>
       </c>
       <c r="N116" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N117" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="M118" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M127" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N127" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.12</v>
+        <v>1.68</v>
       </c>
       <c r="M136" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="N136" t="n">
-        <v>2.48</v>
+        <v>4.7</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,16 +16644,16 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.81</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N29" t="n">
-        <v>1.68</v>
+        <v>3.65</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>2.44</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.23</v>
+        <v>7.4</v>
       </c>
       <c r="M57" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="N57" t="n">
-        <v>11</v>
+        <v>1.42</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7.4</v>
+        <v>1.23</v>
       </c>
       <c r="M59" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="N59" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="M61" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.55</v>
+        <v>1.96</v>
       </c>
       <c r="M62" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.8</v>
+        <v>1.82</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="M66" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N69" t="n">
-        <v>4.3</v>
+        <v>2.35</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N71" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N72" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N74" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.82</v>
+        <v>2.6</v>
       </c>
       <c r="M75" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.85</v>
+        <v>1.6</v>
       </c>
       <c r="M78" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N78" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.72</v>
+        <v>2.9</v>
       </c>
       <c r="M82" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="M83" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N83" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N84" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.01</v>
+        <v>2.85</v>
       </c>
       <c r="M88" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="M89" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N89" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="M93" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N93" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.21</v>
+        <v>2.95</v>
       </c>
       <c r="M94" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N94" t="n">
-        <v>3.15</v>
+        <v>2.29</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="M98" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N98" t="n">
-        <v>4.9</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="M116" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="M117" t="n">
-        <v>3.21</v>
+        <v>3.72</v>
       </c>
       <c r="N117" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N118" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M126" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N126" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,16 +16055,16 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,16 +16174,16 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.2</v>
+        <v>1.86</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.11</v>
+        <v>3.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>7.4</v>
+        <v>1.23</v>
       </c>
       <c r="M57" t="n">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="N57" t="n">
-        <v>1.42</v>
+        <v>11</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,16 +7249,16 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE57" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.23</v>
+        <v>7.4</v>
       </c>
       <c r="M59" t="n">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="N59" t="n">
-        <v>11</v>
+        <v>1.42</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="M61" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N61" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N62" t="n">
-        <v>3.75</v>
+        <v>3.26</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="M64" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="M65" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="N65" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.77</v>
+        <v>3.5</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="N66" t="n">
-        <v>4.3</v>
+        <v>1.88</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.75</v>
+        <v>1.78</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N67" t="n">
-        <v>1.93</v>
+        <v>3.97</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.72</v>
+        <v>2.33</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N68" t="n">
-        <v>4.5</v>
+        <v>2.85</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="M69" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.35</v>
+        <v>3.47</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N70" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="M71" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.15</v>
+        <v>2.49</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="M72" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N72" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.82</v>
+        <v>2.95</v>
       </c>
       <c r="M74" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N74" t="n">
-        <v>4.3</v>
+        <v>2.29</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N75" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,55 +9584,55 @@
         </is>
       </c>
       <c r="L77" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB77" t="n">
         <v>2</v>
-      </c>
-      <c r="M77" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N77" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>1.62</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="M78" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.9</v>
+        <v>1.93</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="N82" t="n">
-        <v>2.37</v>
+        <v>3.53</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="M83" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="N83" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="M84" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N84" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.33</v>
+        <v>3.55</v>
       </c>
       <c r="M85" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N85" t="n">
-        <v>2.85</v>
+        <v>1.95</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N87" t="n">
-        <v>4.9</v>
+        <v>2.49</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.85</v>
+        <v>2.47</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N88" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N89" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N99" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N116" t="n">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="M117" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M131" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="N131" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,16 +16055,16 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC131" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,16 +16174,16 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC132" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="M142" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N142" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD142" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,14 +17438,14 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="M143" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N143" t="n">
         <v>6.5</v>
       </c>
-      <c r="N143" t="n">
-        <v>13</v>
-      </c>
       <c r="O143" t="n">
         <v>0</v>
       </c>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC143" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.81</v>
+        <v>1.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7683,10 +7683,10 @@
         <v>2.33</v>
       </c>
       <c r="M61" t="n">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="M62" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="N62" t="n">
-        <v>3.26</v>
+        <v>3.97</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.77</v>
+        <v>1.82</v>
       </c>
       <c r="M64" t="n">
-        <v>3.09</v>
+        <v>3.75</v>
       </c>
       <c r="N64" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="M65" t="n">
-        <v>3.37</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.5</v>
+        <v>1.72</v>
       </c>
       <c r="M66" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="N66" t="n">
-        <v>1.88</v>
+        <v>4.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="M67" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="N67" t="n">
-        <v>3.97</v>
+        <v>3.26</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.96</v>
+        <v>2.95</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>3.47</v>
+        <v>2.29</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="N71" t="n">
-        <v>2.49</v>
+        <v>1.88</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="M74" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>2.29</v>
+        <v>3.25</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.81</v>
+        <v>2.4</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="M77" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="M78" t="n">
         <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>2.6</v>
+        <v>3.47</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N79" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N81" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M86" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N86" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="M87" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N87" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.47</v>
+        <v>2.85</v>
       </c>
       <c r="M88" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="N88" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="M91" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N91" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB91" t="n">
         <v>2</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="M92" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.47</v>
+        <v>2.33</v>
       </c>
       <c r="M95" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="N95" t="n">
-        <v>6.8</v>
+        <v>2.78</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M96" t="n">
         <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>3.45</v>
+        <v>2.49</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11967,10 +11967,10 @@
         <v>2.8</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N97" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.4</v>
+        <v>1.66</v>
       </c>
       <c r="M99" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N99" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,55 +16010,55 @@
         </is>
       </c>
       <c r="L131" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M131" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="N131" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB131" t="n">
         <v>1.68</v>
-      </c>
-      <c r="M131" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N131" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>1.63</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.72</v>
+        <v>3.12</v>
       </c>
       <c r="M132" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="N132" t="n">
-        <v>4.4</v>
+        <v>2.48</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16168,22 +16168,22 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD132" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,16 +16531,16 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC135" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD135" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G146" t="n">

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>3.81</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.96</v>
+        <v>3.19</v>
       </c>
       <c r="M44" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.73</v>
+        <v>7.4</v>
       </c>
       <c r="M58" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="N58" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7368,10 +7368,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>7.4</v>
+        <v>1.73</v>
       </c>
       <c r="M59" t="n">
-        <v>4.4</v>
+        <v>3.61</v>
       </c>
       <c r="N59" t="n">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="M62" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N62" t="n">
-        <v>3.97</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.82</v>
+        <v>2.85</v>
       </c>
       <c r="M64" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>4.3</v>
+        <v>2.49</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M66" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="N66" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.99</v>
+        <v>3.55</v>
       </c>
       <c r="M67" t="n">
-        <v>3.21</v>
+        <v>3.85</v>
       </c>
       <c r="N67" t="n">
-        <v>3.26</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.95</v>
+        <v>1.47</v>
       </c>
       <c r="M69" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="N69" t="n">
-        <v>2.29</v>
+        <v>6.8</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.55</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>1.95</v>
+        <v>4.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="N74" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N76" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="M77" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N78" t="n">
-        <v>3.47</v>
+        <v>4.3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M79" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N79" t="n">
         <v>3.5</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="M81" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N81" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N84" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N86" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.6</v>
+        <v>2.33</v>
       </c>
       <c r="M87" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N87" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="N88" t="n">
-        <v>2.49</v>
+        <v>4.5</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="M89" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N89" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="M90" t="n">
-        <v>3.02</v>
+        <v>3.31</v>
       </c>
       <c r="N90" t="n">
-        <v>2.61</v>
+        <v>1.88</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M91" t="n">
-        <v>3.9</v>
+        <v>3.37</v>
       </c>
       <c r="N91" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB91" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.1</v>
+        <v>2.77</v>
       </c>
       <c r="M93" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N93" t="n">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="M94" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>3.53</v>
+        <v>2.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.33</v>
+        <v>1.66</v>
       </c>
       <c r="M95" t="n">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="N95" t="n">
-        <v>2.78</v>
+        <v>4.9</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M96" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.8</v>
+        <v>1.99</v>
       </c>
       <c r="M97" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="N97" t="n">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="M98" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N98" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="M99" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N99" t="n">
-        <v>4.9</v>
+        <v>2.49</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N117" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M118" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="M125" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="N125" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC129" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD129" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,16 +16531,16 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD135" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>2.62</v>
+        <v>3.9</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>3.19</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="N68" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="M69" t="n">
-        <v>4.2</v>
+        <v>3.31</v>
       </c>
       <c r="N69" t="n">
-        <v>6.8</v>
+        <v>1.88</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB69" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.9</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="M70" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N70" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>2.8</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N73" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="M74" t="n">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="N74" t="n">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.93</v>
+        <v>3.55</v>
       </c>
       <c r="M75" t="n">
-        <v>3.14</v>
+        <v>3.85</v>
       </c>
       <c r="N75" t="n">
-        <v>3.53</v>
+        <v>1.95</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,10 +9465,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M76" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N76" t="n">
         <v>3.5</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="M78" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M79" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N79" t="n">
-        <v>3.5</v>
+        <v>2.29</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.13</v>
+        <v>2.47</v>
       </c>
       <c r="M81" t="n">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="N81" t="n">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="M82" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="N82" t="n">
-        <v>3.15</v>
+        <v>3.53</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AB82" t="n">
         <v>1.68</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N83" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="M84" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N84" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="M86" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="N86" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="M89" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N89" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="M90" t="n">
-        <v>3.31</v>
+        <v>3.8</v>
       </c>
       <c r="N90" t="n">
-        <v>1.88</v>
+        <v>4.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="M91" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="N91" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N92" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="M93" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N94" t="n">
-        <v>2.6</v>
+        <v>3.26</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.99</v>
+        <v>2.21</v>
       </c>
       <c r="M97" t="n">
-        <v>3.21</v>
+        <v>2.95</v>
       </c>
       <c r="N97" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N98" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M99" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N99" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="M116" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.79</v>
+        <v>2.35</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="M117" t="n">
-        <v>3.21</v>
+        <v>3.72</v>
       </c>
       <c r="N117" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N118" t="n">
-        <v>3.59</v>
+        <v>4.2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M129" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="N129" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,16 +15817,16 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="AC129" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD129" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,16 +16055,16 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16168,10 +16168,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16644,10 +16644,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,14 +17319,14 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="M142" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N142" t="n">
         <v>6.5</v>
       </c>
-      <c r="N142" t="n">
-        <v>13</v>
-      </c>
       <c r="O142" t="n">
         <v>0</v>
       </c>
@@ -17364,16 +17364,16 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="AC142" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="M143" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="N143" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,16 +17483,16 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD143" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
       </c>
       <c r="AE143" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>

--- a/jogos_2026-01-04.xlsx
+++ b/jogos_2026-01-04.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>3.81</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>1.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.26</v>
+        <v>1.6</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSBS Biak Numfor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N40" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>PSBS Biak Numfor</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="M61" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N61" t="n">
-        <v>3.47</v>
+        <v>3.97</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7725,10 +7725,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,13 +7799,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.68</v>
+        <v>2.21</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>2.95</v>
       </c>
       <c r="N62" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7844,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -7963,10 +7963,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.85</v>
+        <v>1.6</v>
       </c>
       <c r="M64" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N64" t="n">
-        <v>2.49</v>
+        <v>5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>1.47</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8201,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M68" t="n">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="N68" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,14 +8632,14 @@
         </is>
       </c>
       <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N69" t="n">
         <v>3.5</v>
       </c>
-      <c r="M69" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1.88</v>
-      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="M70" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>1.88</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="M72" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>3.97</v>
+        <v>2.94</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>3.09</v>
       </c>
       <c r="N73" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.77</v>
+        <v>1.99</v>
       </c>
       <c r="M74" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="N74" t="n">
-        <v>2.3</v>
+        <v>3.26</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.55</v>
+        <v>2.33</v>
       </c>
       <c r="M75" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N75" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.07</v>
+        <v>3.55</v>
       </c>
       <c r="M76" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N76" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="M77" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N77" t="n">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.81</v>
+        <v>5.3</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>3.9</v>
+        <v>1.66</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.95</v>
+        <v>2.13</v>
       </c>
       <c r="M79" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N79" t="n">
-        <v>2.29</v>
+        <v>3.25</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="M80" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N80" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="M81" t="n">
-        <v>3.02</v>
+        <v>3.75</v>
       </c>
       <c r="N81" t="n">
-        <v>2.61</v>
+        <v>4.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10108,7 +10108,7 @@
         <v>2</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="M83" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="N83" t="n">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="M84" t="n">
-        <v>3.75</v>
+        <v>3.14</v>
       </c>
       <c r="N84" t="n">
-        <v>4.3</v>
+        <v>3.53</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.47</v>
+        <v>2.95</v>
       </c>
       <c r="M85" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N85" t="n">
-        <v>6.8</v>
+        <v>2.29</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.9</v>
+        <v>1.96</v>
       </c>
       <c r="M89" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N89" t="n">
-        <v>2.37</v>
+        <v>3.47</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="M90" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N90" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="M91" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N91" t="n">
-        <v>3.45</v>
+        <v>2.37</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="M92" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N92" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="M93" t="n">
         <v>3.3</v>
       </c>
       <c r="N93" t="n">
-        <v>2.49</v>
+        <v>3.45</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="M94" t="n">
-        <v>3.21</v>
+        <v>3.9</v>
       </c>
       <c r="N94" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11652,10 +11652,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="M97" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="N97" t="n">
-        <v>3.15</v>
+        <v>2.61</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="M98" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="N98" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M99" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N99" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N116" t="n">
-        <v>3.59</v>
+        <v>4.4</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="M117" t="n">
-        <v>3.72</v>
+        <v>3.21</v>
       </c>
       <c r="N117" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="M118" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>4.2</v>
+        <v>3.59</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="M126" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="N126" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="M127" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="N127" t="n">
-        <v>2.84</v>
+        <v>2.05</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,16 +16055,16 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD131" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Manchester City</t>
         </is>
       </c>
  